--- a/etl/data/inputs/Shell White Oil Tank Cleaning Guide - procedure template steps.xlsx
+++ b/etl/data/inputs/Shell White Oil Tank Cleaning Guide - procedure template steps.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="109">
   <si>
     <t xml:space="preserve">procedure_code</t>
   </si>
@@ -85,58 +85,37 @@
     <t xml:space="preserve">Flush tank bottoms with sea water, drain well and gas free to 40% of lower explosive limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Flush, gas free, lift scale and mop</t>
+    <t xml:space="preserve">Flush tank bottoms</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixed machine full wash – 1 cycle</t>
+    <t xml:space="preserve">Remove remaining cargo/residue from the bottom of the tank.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot Sea Water</t>
+    <t xml:space="preserve">Gas free</t>
   </si>
   <si>
-    <t xml:space="preserve">75–80°C</t>
+    <t xml:space="preserve">Ventilate the tank and make sure it is safe and free from hazardous vapours</t>
   </si>
   <si>
-    <t xml:space="preserve">60 min/group</t>
+    <t xml:space="preserve">Lift scale</t>
   </si>
   <si>
-    <t xml:space="preserve">Washing</t>
+    <t xml:space="preserve">Remove/lift any scale, deposits, or hardened residue from the tank surfaces.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot Fresh Water</t>
+    <t xml:space="preserve">Mop up</t>
   </si>
   <si>
-    <t xml:space="preserve">Ventilate</t>
+    <t xml:space="preserve">Manually wipe and collect the remaining liquid/residue.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ventilation</t>
+    <t xml:space="preserve">Drain the pipelines,valves,pumps</t>
   </si>
   <si>
-    <t xml:space="preserve">Air / Ventilation</t>
+    <t xml:space="preserve">For lubricating oil or naphthenic distillate</t>
   </si>
   <si>
     <t xml:space="preserve">60 min/tank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hand washing / flushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot, if required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mopping</t>
   </si>
   <si>
     <t xml:space="preserve">Cold machine wash</t>
@@ -566,11 +545,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U1048576"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="37.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="56.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="85.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
@@ -745,15 +724,9 @@
       <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="n">
         <v>1</v>
@@ -778,21 +751,15 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -815,19 +782,15 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -850,21 +813,15 @@
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -887,11 +844,11 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -914,26 +871,34 @@
     </row>
     <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -945,35 +910,33 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -988,31 +951,29 @@
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1025,21 +986,21 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -1049,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -1062,21 +1023,21 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -1104,16 +1065,16 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -1123,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1136,21 +1097,21 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -1160,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1178,18 +1139,20 @@
         <v>7</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1197,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -1215,19 +1178,19 @@
         <v>7</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1236,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1254,19 +1217,19 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -1275,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1288,25 +1251,23 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -1314,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -1327,23 +1288,25 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1351,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -1364,24 +1327,24 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1390,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1403,24 +1366,24 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1429,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1442,33 +1405,33 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1486,28 +1449,30 @@
         <v>8</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1525,30 +1490,28 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1566,28 +1529,26 @@
         <v>8</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1600,31 +1561,33 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -1637,25 +1600,23 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -1663,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -1681,16 +1642,16 @@
         <v>8</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1700,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -1713,23 +1674,25 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -1737,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -1750,25 +1713,23 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
         <v>8</v>
       </c>
       <c r="B32" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -1776,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -1789,21 +1750,21 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -1813,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -1826,23 +1787,25 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -1850,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -1863,24 +1826,24 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -1889,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -1902,24 +1865,24 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -1928,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -1941,33 +1904,33 @@
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -1985,28 +1948,30 @@
         <v>9</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -2024,30 +1989,28 @@
         <v>9</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -2065,28 +2028,26 @@
         <v>9</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -2099,31 +2060,33 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -2136,25 +2099,23 @@
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -2162,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -2180,16 +2141,16 @@
         <v>9</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2199,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2212,23 +2173,25 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
     </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -2236,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2249,25 +2212,23 @@
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
     </row>
-    <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B45" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -2275,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -2288,32 +2249,18 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
     </row>
-    <row r="46" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>115</v>
-      </c>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -24267,29 +24214,7 @@
       <c r="T1000" s="2"/>
       <c r="U1000" s="2"/>
     </row>
-    <row r="1001" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="2"/>
-      <c r="B1001" s="2"/>
-      <c r="C1001" s="2"/>
-      <c r="D1001" s="2"/>
-      <c r="E1001" s="2"/>
-      <c r="F1001" s="2"/>
-      <c r="G1001" s="2"/>
-      <c r="H1001" s="2"/>
-      <c r="I1001" s="2"/>
-      <c r="J1001" s="2"/>
-      <c r="K1001" s="2"/>
-      <c r="L1001" s="2"/>
-      <c r="M1001" s="2"/>
-      <c r="N1001" s="2"/>
-      <c r="O1001" s="2"/>
-      <c r="P1001" s="2"/>
-      <c r="Q1001" s="2"/>
-      <c r="R1001" s="2"/>
-      <c r="S1001" s="2"/>
-      <c r="T1001" s="2"/>
-      <c r="U1001" s="2"/>
-    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
